--- a/results/full_medical_lgbm_summary/medical_PartialAbstention_summary.xlsx
+++ b/results/full_medical_lgbm_summary/medical_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.1970±0.0116</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.2125±0.0207</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.2571±0.0122</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.2995±0.0241</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9708±0.0125</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9484±0.0011</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8548±0.0067</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.7336±0.0009</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5704±0.1441</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.4474±0.0242</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.1962±0.0141</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.0901±0.0077</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.8787±0.0156</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.8862±0.0153</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.8719±0.0137</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.8012±0.0397</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6537±0.1053</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5498±0.0197</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.2937±0.0142</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.1547±0.0084</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.9685±0.0133</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.9427±0.0012</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.8434±0.0073</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.7203±0.0023</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5544±0.1373</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.4380±0.0222</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.1932±0.0134</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.0895±0.0078</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.3935±0.0328</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.2394±0.0154</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.1519±0.0083</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0998±0.0026</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.3716±0.0304</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.1801±0.0105</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1017±0.0066</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0629±0.0017</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.4565±0.0471</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.4300±0.0589</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.4329±0.0301</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.4063±0.0321</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9738±0.0056</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9075±0.0187</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7904±0.0196</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6357±0.1011</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.4806±0.0115</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.2454±0.0079</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1406±0.0052</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5087±0.1319</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.3282±0.0105</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.1429±0.0054</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.0771±0.0028</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.8853±0.0183</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.8984±0.0162</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.8694±0.0118</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7984±0.0407</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.2985±0.2072</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.1850±0.0275</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.0317±0.0104</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.0082±0.0069</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.2920±0.2025</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.1800±0.0264</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.0267±0.0104</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0061±0.0075</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.1866±0.0201</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.2142±0.0176</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2792±0.0167</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.3374±0.0138</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9671±0.0152</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9211±0.0031</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.8014±0.0098</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.6621±0.0062</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5381±0.1536</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.3461±0.0313</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.1556±0.0150</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.0789±0.0071</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8874±0.0131</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.8963±0.0119</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.8933±0.0171</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.8569±0.0261</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6315±0.1158</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.4547±0.0262</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.2414±0.0156</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.1373±0.0071</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.9646±0.0163</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.9121±0.0037</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7853±0.0100</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6449±0.0045</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5243±0.1469</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.3395±0.0282</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.1532±0.0139</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.0786±0.0070</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.3931±0.0310</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.2051±0.0117</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.1305±0.0060</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.0916±0.0020</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.3642±0.0279</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.1465±0.0088</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.0839±0.0046</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0559±0.0015</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.4707±0.0514</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.4456±0.0573</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.4611±0.0246</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.4612±0.0370</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9559±0.0127</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.8546±0.0205</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7174±0.0121</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6141±0.1078</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.3801±0.0146</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.1964±0.0090</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1220±0.0034</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.4795±0.1290</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.2404±0.0118</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.1104±0.0057</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.0657±0.0019</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.8964±0.0161</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.9095±0.0143</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.8926±0.0108</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.8598±0.0269</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.2515±0.2071</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.1094±0.0281</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.0245±0.0113</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0082±0.0069</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.2444±0.2018</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.1039±0.0270</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.0195±0.0114</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.0061±0.0075</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.2019±0.0136</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.2179±0.0264</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.2621±0.0165</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.2926±0.0236</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9692±0.0151</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9499±0.0011</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8562±0.0061</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.7353±0.0008</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.5599±0.1652</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.4540±0.0264</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.1948±0.0147</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.0900±0.0076</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.8741±0.0188</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.8841±0.0172</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.8666±0.0118</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.7981±0.0399</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6434±0.1211</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5556±0.0219</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.2924±0.0144</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.1547±0.0081</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.9668±0.0161</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.9443±0.0013</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.8448±0.0067</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.7221±0.0022</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5423±0.1576</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.4446±0.0247</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.1918±0.0139</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.0895±0.0076</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.3954±0.0335</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.2419±0.0174</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.1510±0.0079</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.1004±0.0022</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.3800±0.0321</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.1831±0.0118</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1011±0.0060</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0633±0.0014</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.4534±0.0483</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.4271±0.0617</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.4240±0.0267</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.4121±0.0342</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9737±0.0057</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9073±0.0154</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.7837±0.0279</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6270±0.1145</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.4872±0.0130</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2461±0.0080</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1411±0.0049</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.5033±0.1465</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.3348±0.0114</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.1435±0.0054</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.0774±0.0026</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.8793±0.0226</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.8950±0.0187</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.8644±0.0121</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7967±0.0394</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.2822±0.2376</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.1902±0.0288</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.0307±0.0111</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.0082±0.0069</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.2758±0.2330</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.1852±0.0283</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.0257±0.0107</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.0061±0.0075</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.1865±0.0200</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.2192±0.0218</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.2800±0.0162</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.3375±0.0104</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9672±0.0151</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9208±0.0030</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.8005±0.0094</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.6587±0.0060</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.5382±0.1534</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.3459±0.0319</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.1549±0.0150</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.0783±0.0070</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.8881±0.0135</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.8958±0.0125</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.8887±0.0179</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.8560±0.0274</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6317±0.1155</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.4543±0.0267</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.2403±0.0154</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.1363±0.0068</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.9647±0.0162</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.9117±0.0036</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7841±0.0096</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6412±0.0039</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5244±0.1466</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.3394±0.0288</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.1526±0.0139</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.0780±0.0069</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.3932±0.0310</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.2044±0.0126</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.1290±0.0058</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.0909±0.0016</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.3642±0.0279</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.1462±0.0096</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.0828±0.0045</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0555±0.0013</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.4710±0.0515</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.4434±0.0589</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.4584±0.0278</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.4575±0.0522</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9571±0.0146</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.8510±0.0197</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.7163±0.0127</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.6146±0.1072</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.3790±0.0144</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.1947±0.0086</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1208±0.0025</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.4797±0.1287</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.2396±0.0115</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.1094±0.0054</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.0650±0.0015</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.8980±0.0164</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.9079±0.0160</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.8876±0.0131</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.8598±0.0270</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.2515±0.2071</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.1094±0.0281</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.0245±0.0113</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.0082±0.0069</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.2444±0.2018</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.1039±0.0270</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.0195±0.0114</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.0061±0.0075</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.1978±0.0115</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.2247±0.0259</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.2566±0.0177</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.2950±0.0196</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9710±0.0125</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9515±0.0013</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8738±0.0074</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7746±0.0016</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.5749±0.1469</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.4615±0.0205</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.2233±0.0229</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.1039±0.0082</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.8755±0.0160</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.8758±0.0179</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.8543±0.0125</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.7731±0.0367</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.6555±0.1066</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.5599±0.0173</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.3223±0.0220</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.1752±0.0095</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.9688±0.0134</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.9474±0.0013</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8688±0.0082</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7720±0.0020</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5567±0.1392</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4488±0.0198</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.2187±0.0215</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.1024±0.0085</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.3953±0.0339</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.2407±0.0158</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.1592±0.0099</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1077±0.0020</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.3760±0.0328</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.1839±0.0100</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1090±0.0076</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0695±0.0012</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.4556±0.0476</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.4170±0.0600</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.4128±0.0214</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.3772±0.0280</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9812±0.0056</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9201±0.0140</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8308±0.0160</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.6374±0.1024</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.4926±0.0112</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.2689±0.0129</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1582±0.0053</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.5129±0.1351</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.3419±0.0100</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.1599±0.0089</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.0882±0.0028</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.8806±0.0197</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.8819±0.0181</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.8472±0.0165</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.7677±0.0379</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.3016±0.2111</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.1942±0.0292</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.0378±0.0135</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0041±0.0060</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.2952±0.2066</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.1884±0.0285</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.0358±0.0151</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0041±0.0060</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.1906±0.0119</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.2306±0.0215</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.2727±0.0177</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.3602±0.0206</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9675±0.0150</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9197±0.0025</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.8007±0.0093</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.6199±0.0110</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.5415±0.1540</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.3422±0.0247</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.1508±0.0120</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.0700±0.0049</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.8844±0.0128</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.8874±0.0147</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.8871±0.0165</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.8705±0.0219</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6332±0.1141</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.4484±0.0200</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.2373±0.0128</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.1257±0.0066</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.9650±0.0161</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.9131±0.0028</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.7924±0.0106</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6149±0.0120</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.5264±0.1461</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.3337±0.0209</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.1486±0.0113</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.0696±0.0049</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.3933±0.0290</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.2006±0.0098</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.1292±0.0065</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.0863±0.0025</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.3672±0.0266</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.1442±0.0067</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.0832±0.0048</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0521±0.0018</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.4659±0.0498</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.4267±0.0558</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.4573±0.0215</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.4768±0.0513</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9547±0.0192</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8562±0.0162</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.6693±0.0295</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.6163±0.1062</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.3734±0.0118</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.1952±0.0081</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1120±0.0037</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.4843±0.1312</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.2359±0.0091</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.1097±0.0050</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.0599±0.0021</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.8916±0.0173</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.8961±0.0164</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.8851±0.0225</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.8685±0.0205</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.2546±0.2110</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.1053±0.0221</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.0174±0.0076</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0010±0.0020</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.2476±0.2058</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.0988±0.0225</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.0154±0.0079</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0010±0.0020</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.2070±0.0058</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.2241±0.0272</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.2729±0.0247</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.2931±0.0197</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9693±0.0150</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9560±0.0013</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8825±0.0063</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.7886±0.0010</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.5628±0.1664</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.4929±0.0174</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.2415±0.0235</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.1105±0.0088</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.8687±0.0187</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.8698±0.0170</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.8402±0.0126</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.7715±0.0419</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.6431±0.1197</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5841±0.0151</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.3394±0.0217</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.1847±0.0108</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.9670±0.0160</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.9524±0.0013</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.8778±0.0070</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7860±0.0018</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5422±0.1559</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4790±0.0175</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.2361±0.0228</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.1089±0.0091</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.3949±0.0331</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.2482±0.0174</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.1613±0.0112</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1110±0.0018</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.3862±0.0356</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.1922±0.0116</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1118±0.0085</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0722±0.0008</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.4482±0.0480</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.4144±0.0606</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3896±0.0229</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.3739±0.0299</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9801±0.0056</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9245±0.0129</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8482±0.0123</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.6268±0.1125</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.5155±0.0096</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.2796±0.0127</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1663±0.0062</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.5061±0.1463</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.3654±0.0092</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.1681±0.0089</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.0933±0.0034</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.8713±0.0229</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.8759±0.0169</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.8329±0.0200</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.7643±0.0389</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.2822±0.2346</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.2321±0.0256</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.0531±0.0163</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0041±0.0060</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.2759±0.2298</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.2266±0.0255</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.0512±0.0181</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0041±0.0060</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.1906±0.0119</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.2323±0.0190</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.2756±0.0183</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.3472±0.0188</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9675±0.0150</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9204±0.0025</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.8027±0.0094</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.6266±0.0079</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.5415±0.1540</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.3436±0.0252</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.1516±0.0123</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.0699±0.0046</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.8844±0.0128</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.8853±0.0140</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.8871±0.0164</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.8572±0.0332</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6332±0.1141</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.4494±0.0208</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.2383±0.0132</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.1255±0.0062</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.9650±0.0161</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.9138±0.0029</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.7942±0.0106</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.6213±0.0085</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5264±0.1461</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.3350±0.0213</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.1494±0.0116</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.0695±0.0047</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.3932±0.0289</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.2008±0.0106</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.1298±0.0069</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.0860±0.0020</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.3669±0.0264</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.1447±0.0077</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.0836±0.0051</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0521±0.0015</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.4659±0.0498</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.4249±0.0554</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.4533±0.0306</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.4616±0.0549</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9558±0.0181</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8582±0.0125</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.6765±0.0315</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.6163±0.1062</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.3748±0.0119</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.1968±0.0085</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1121±0.0032</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.4843±0.1312</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.2372±0.0093</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.1107±0.0053</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.0600±0.0018</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.8916±0.0173</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.8936±0.0139</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.8851±0.0205</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.8554±0.0283</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.2546±0.2110</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.1063±0.0206</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.0174±0.0076</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0010±0.0020</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.2476±0.2058</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.0998±0.0211</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.0154±0.0079</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0010±0.0020</t>
         </is>
